--- a/油价调整日历.xlsx
+++ b/油价调整日历.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3319,154 +3319,154 @@
       <c r="A19" s="4" t="n">
         <v>46276</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="M19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="N19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="O19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="P19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="Q19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="R19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="S19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="T19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="U19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="V19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="W19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="X19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="Y19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="Z19" s="14" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AA19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AB19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AC19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AD19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AE19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="Y19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AA19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AB19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AC19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AD19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AE19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>

--- a/油价调整日历.xlsx
+++ b/油价调整日历.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE26"/>
+  <dimension ref="A1:AV26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -679,6 +679,91 @@
           <t>青海省</t>
         </is>
       </c>
+      <c r="AF1" s="0" t="inlineStr">
+        <is>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AG1" s="0" t="inlineStr">
+        <is>
+          <t>辽宁省-大连市</t>
+        </is>
+      </c>
+      <c r="AH1" s="0" t="inlineStr">
+        <is>
+          <t>山东省-青岛市</t>
+        </is>
+      </c>
+      <c r="AI1" s="0" t="inlineStr">
+        <is>
+          <t>福建省-厦门市</t>
+        </is>
+      </c>
+      <c r="AJ1" s="0" t="inlineStr">
+        <is>
+          <t>浙江省-宁波市</t>
+        </is>
+      </c>
+      <c r="AK1" s="0" t="inlineStr">
+        <is>
+          <t>西藏-拉萨市</t>
+        </is>
+      </c>
+      <c r="AL1" s="0" t="inlineStr">
+        <is>
+          <t>新疆-乌鲁木齐市</t>
+        </is>
+      </c>
+      <c r="AM1" s="0" t="inlineStr">
+        <is>
+          <t>新疆-克拉玛依市</t>
+        </is>
+      </c>
+      <c r="AN1" s="0" t="inlineStr">
+        <is>
+          <t>内蒙古-呼和浩特市</t>
+        </is>
+      </c>
+      <c r="AO1" s="0" t="inlineStr">
+        <is>
+          <t>四川省-甘孜藏族自治州</t>
+        </is>
+      </c>
+      <c r="AP1" s="0" t="inlineStr">
+        <is>
+          <t>四川省-阿坝藏族羌族自治州</t>
+        </is>
+      </c>
+      <c r="AQ1" s="0" t="inlineStr">
+        <is>
+          <t>四川省-凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="AR1" s="0" t="inlineStr">
+        <is>
+          <t>云南省-迪庆藏族自治州</t>
+        </is>
+      </c>
+      <c r="AS1" s="0" t="inlineStr">
+        <is>
+          <t>云南省-怒江傈僳族自治州</t>
+        </is>
+      </c>
+      <c r="AT1" s="0" t="inlineStr">
+        <is>
+          <t>青海省-玉树藏族自治州</t>
+        </is>
+      </c>
+      <c r="AU1" s="0" t="inlineStr">
+        <is>
+          <t>青海省-果洛藏族自治州</t>
+        </is>
+      </c>
+      <c r="AV1" s="0" t="inlineStr">
+        <is>
+          <t>甘肃省-甘南藏族自治州</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -834,6 +919,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -989,6 +1159,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1144,6 +1399,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1299,6 +1639,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1454,6 +1879,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1609,6 +2119,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1764,6 +2359,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1919,6 +2599,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -2074,6 +2839,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2229,6 +3079,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2384,6 +3319,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2539,6 +3559,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -2694,6 +3799,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2849,6 +4039,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -3004,6 +4279,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -3159,6 +4519,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -3314,6 +4759,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -3469,6 +4999,91 @@
           <t>√</t>
         </is>
       </c>
+      <c r="AF19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -3624,6 +5239,91 @@
           <t>未调整</t>
         </is>
       </c>
+      <c r="AF20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV20" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -3779,6 +5479,91 @@
           <t>未调整</t>
         </is>
       </c>
+      <c r="AF21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV21" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -3934,6 +5719,91 @@
           <t>未调整</t>
         </is>
       </c>
+      <c r="AF22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV22" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4089,6 +5959,91 @@
           <t>未调整</t>
         </is>
       </c>
+      <c r="AF23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV23" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -4244,6 +6199,91 @@
           <t>未调整</t>
         </is>
       </c>
+      <c r="AF24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV24" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -4399,6 +6439,91 @@
           <t>未调整</t>
         </is>
       </c>
+      <c r="AF25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV25" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4550,6 +6675,91 @@
         </is>
       </c>
       <c r="AE26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AF26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU26" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV26" s="13" t="inlineStr">
         <is>
           <t>未调整</t>
         </is>

--- a/油价调整日历.xlsx
+++ b/油价调整日历.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/油价调整日历.xlsx
+++ b/油价调整日历.xlsx
@@ -919,89 +919,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV2" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV2" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -1159,89 +1159,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV3" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV3" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -1399,89 +1399,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV4" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV4" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -1639,89 +1639,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV5" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV5" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -1879,89 +1879,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV6" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV6" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -2119,89 +2119,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV7" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV7" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -2359,89 +2359,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV8" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV8" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -2599,89 +2599,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV9" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV9" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -2839,89 +2839,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV10" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV10" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -3079,89 +3079,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV11" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV11" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -3319,89 +3319,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV12" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV12" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -3559,89 +3559,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV13" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV13" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -3799,89 +3799,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV14" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV14" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -4039,89 +4039,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV15" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV15" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -4279,89 +4279,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV16" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV16" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -4519,89 +4519,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV17" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV17" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -4759,89 +4759,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV18" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV18" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
@@ -4999,89 +4999,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AG19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AH19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AI19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AJ19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AK19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AL19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AM19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AN19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AO19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AP19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AQ19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AR19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AS19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AT19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AU19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
-        </is>
-      </c>
-      <c r="AV19" s="13" t="inlineStr">
-        <is>
-          <t>未调整</t>
+      <c r="AF19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AG19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AH19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AI19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AJ19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AK19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AL19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AM19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AN19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AO19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AP19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AQ19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AR19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AS19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AT19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AU19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="AV19" s="11" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>

--- a/油价调整日历.xlsx
+++ b/油价调整日历.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -919,89 +919,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV2" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV2" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -1159,89 +1159,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV3" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV3" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -1399,89 +1399,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV4" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV4" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -1639,89 +1639,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV5" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV5" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -1879,89 +1879,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV6" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV6" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -2119,89 +2119,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV7" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV7" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -2359,89 +2359,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV8" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV8" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -2599,89 +2599,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV9" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV9" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -2839,89 +2839,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV10" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV10" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -3079,89 +3079,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV11" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV11" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -3319,89 +3319,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV12" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV12" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -3559,89 +3559,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV13" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV13" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -3799,89 +3799,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV14" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV14" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -4039,89 +4039,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV15" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV15" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -4279,89 +4279,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV16" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV16" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -4519,89 +4519,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV17" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV17" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -4759,89 +4759,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV18" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV18" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
@@ -4999,89 +4999,89 @@
           <t>√</t>
         </is>
       </c>
-      <c r="AF19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AG19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AH19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AI19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AJ19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AK19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AL19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AM19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AN19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AO19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AP19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AQ19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AR19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AS19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AT19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AU19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="AV19" s="11" t="inlineStr">
-        <is>
-          <t>√</t>
+      <c r="AF19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AG19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AH19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AI19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AJ19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AK19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AL19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AM19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AN19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AO19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AP19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AQ19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AR19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AS19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AT19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AU19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
+        </is>
+      </c>
+      <c r="AV19" s="13" t="inlineStr">
+        <is>
+          <t>未调整</t>
         </is>
       </c>
     </row>
